--- a/data/trans_orig/IP07A06-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07A06-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse triste en 2007 (tasa de respuesta: 99,7%)</t>
+          <t>Menores según la frecuencia de sentirse triste, percibida por el adulto en 2007 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>10585</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17815</t>
+          <t>17906</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11715</t>
+          <t>12006</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24775</t>
+          <t>24573</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18355</t>
+          <t>18255</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30963</t>
+          <t>31135</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23904</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37932</t>
+          <t>38210</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45487</t>
+          <t>44981</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65286</t>
+          <t>64845</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,77%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26263</t>
+          <t>25763</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38981</t>
+          <t>38884</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31628</t>
+          <t>30804</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45716</t>
+          <t>46043</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60429</t>
+          <t>61188</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>80708</t>
+          <t>80746</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,75%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5094</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7369</t>
+          <t>7433</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>6681</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16773</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8198</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18429</t>
+          <t>19354</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17540</t>
+          <t>17515</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32502</t>
+          <t>31444</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31241</t>
+          <t>31203</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47295</t>
+          <t>47001</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>20741</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34433</t>
+          <t>33707</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54827</t>
+          <t>55433</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76490</t>
+          <t>76772</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43526</t>
+          <t>43940</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59770</t>
+          <t>59868</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49245</t>
+          <t>50075</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64940</t>
+          <t>64609</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97799</t>
+          <t>98002</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>120931</t>
+          <t>120147</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>58,93%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6315</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15254</t>
+          <t>15673</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>13619</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13534</t>
+          <t>13624</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>26041</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16803</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28233</t>
+          <t>28279</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15530</t>
+          <t>16019</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28371</t>
+          <t>27982</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34457</t>
+          <t>35739</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52158</t>
+          <t>52554</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,27%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33126</t>
+          <t>32326</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29099</t>
+          <t>29678</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42264</t>
+          <t>42574</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54633</t>
+          <t>54299</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>73112</t>
+          <t>72335</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>15280</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29772</t>
+          <t>29103</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8186</t>
+          <t>8825</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19751</t>
+          <t>20948</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>27020</t>
+          <t>27335</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>45083</t>
+          <t>45596</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26056</t>
+          <t>26086</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22911</t>
+          <t>23597</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38020</t>
+          <t>38010</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39244</t>
+          <t>38717</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60477</t>
+          <t>59920</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>40288</t>
+          <t>40347</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55880</t>
+          <t>56737</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>46604</t>
+          <t>46219</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>62761</t>
+          <t>62061</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>90662</t>
+          <t>91240</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>113649</t>
+          <t>114481</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,89%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>9403</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>10767</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12107</t>
+          <t>12111</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>39075</t>
+          <t>38552</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>60542</t>
+          <t>60319</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>37718</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>58118</t>
+          <t>58730</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>82495</t>
+          <t>82887</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>112019</t>
+          <t>113846</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>90872</t>
+          <t>91428</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>118674</t>
+          <t>118506</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>96718</t>
+          <t>97381</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>124543</t>
+          <t>124045</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>197437</t>
+          <t>194048</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>235025</t>
+          <t>234489</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>144076</t>
+          <t>144292</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>173385</t>
+          <t>172651</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>170498</t>
+          <t>171628</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>201348</t>
+          <t>200630</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>324615</t>
+          <t>324441</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>364313</t>
+          <t>367843</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>55,13%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse triste en 2012 (tasa de respuesta: 98,12%)</t>
+          <t>Menores según la frecuencia de sentirse triste, percibida por el adulto en 2012 (tasa de respuesta: 98,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3310</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13608</t>
+          <t>13818</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17823</t>
+          <t>18680</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13980</t>
+          <t>13616</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28242</t>
+          <t>27624</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18125</t>
+          <t>18588</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31064</t>
+          <t>32156</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18370</t>
+          <t>18696</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32660</t>
+          <t>32575</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40422</t>
+          <t>40498</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58680</t>
+          <t>59133</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,76%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24428</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37880</t>
+          <t>38070</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25733</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40172</t>
+          <t>39971</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>55122</t>
+          <t>53768</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>74400</t>
+          <t>73911</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,45%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>8019</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8800</t>
+          <t>9150</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11678</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23707</t>
+          <t>24523</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13875</t>
+          <t>14682</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27047</t>
+          <t>27473</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30583</t>
+          <t>30182</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47769</t>
+          <t>48295</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23778</t>
+          <t>25098</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39094</t>
+          <t>39695</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27483</t>
+          <t>26641</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42533</t>
+          <t>42434</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56320</t>
+          <t>55239</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77334</t>
+          <t>76949</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34152</t>
+          <t>33352</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49236</t>
+          <t>49004</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33713</t>
+          <t>35431</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50252</t>
+          <t>50377</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73114</t>
+          <t>71580</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94960</t>
+          <t>94346</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,21%</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5281</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10140</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21401</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>9057</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19214</t>
+          <t>19609</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20689</t>
+          <t>21103</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36018</t>
+          <t>36681</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18541</t>
+          <t>18323</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31296</t>
+          <t>30623</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14655</t>
+          <t>14736</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26900</t>
+          <t>26507</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36384</t>
+          <t>36849</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54106</t>
+          <t>53692</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,47%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18455</t>
+          <t>18273</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30338</t>
+          <t>30544</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25716</t>
+          <t>26454</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38754</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47588</t>
+          <t>47632</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66400</t>
+          <t>65134</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>47,88%</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6441,77 +6441,77 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1544</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5318</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>5,71%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2138</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>5427</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>2,94%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1544</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4693</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2138</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>5832</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22562</t>
+          <t>21485</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>12546</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24916</t>
+          <t>26026</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24616</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>42798</t>
+          <t>41646</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19031</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33416</t>
+          <t>34254</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16430</t>
+          <t>16592</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30276</t>
+          <t>30150</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38588</t>
+          <t>39677</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60065</t>
+          <t>60276</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>40954</t>
+          <t>40511</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>57568</t>
+          <t>56717</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40664</t>
+          <t>40885</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>56760</t>
+          <t>57186</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>86875</t>
+          <t>85812</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>110357</t>
+          <t>109253</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,23%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2717</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11219</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>8639</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16123</t>
+          <t>15719</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12268</t>
+          <t>12410</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11167</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19338</t>
+          <t>19401</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>44411</t>
+          <t>44486</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>67642</t>
+          <t>67694</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>52652</t>
+          <t>53180</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>74825</t>
+          <t>76714</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>102382</t>
+          <t>103931</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>137366</t>
+          <t>136977</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>94657</t>
+          <t>94143</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>121373</t>
+          <t>121109</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>87374</t>
+          <t>89127</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>115139</t>
+          <t>115975</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>191556</t>
+          <t>189301</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>228984</t>
+          <t>230097</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>130960</t>
+          <t>131178</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>160358</t>
+          <t>160789</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>143328</t>
+          <t>142362</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>172865</t>
+          <t>171512</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>284481</t>
+          <t>281043</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>325194</t>
+          <t>322562</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,28%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse triste en 2016 (tasa de respuesta: 99,02%)</t>
+          <t>Menores según la frecuencia de sentirse triste, percibida por el adulto en 2016 (tasa de respuesta: 99,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>723</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6560</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>12949</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11107</t>
+          <t>10662</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7839</t>
+          <t>7925</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19961</t>
+          <t>19998</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16938</t>
+          <t>17990</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31084</t>
+          <t>31854</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>14849</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28506</t>
+          <t>27967</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35583</t>
+          <t>36565</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55712</t>
+          <t>54429</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>37,68%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30895</t>
+          <t>30393</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45398</t>
+          <t>45196</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37666</t>
+          <t>37511</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52167</t>
+          <t>51513</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>72709</t>
+          <t>73687</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>93741</t>
+          <t>93187</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,5%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>567</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5297</t>
+          <t>5333</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10223</t>
+          <t>9884</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13148</t>
+          <t>13080</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11682</t>
+          <t>11174</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24182</t>
+          <t>23387</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>15026</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18216</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33206</t>
+          <t>32999</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29635</t>
+          <t>29024</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45028</t>
+          <t>45911</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27026</t>
+          <t>26049</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42160</t>
+          <t>42405</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61511</t>
+          <t>60490</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82759</t>
+          <t>81932</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42337</t>
+          <t>42686</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58078</t>
+          <t>59653</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49769</t>
+          <t>50329</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66983</t>
+          <t>66910</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97844</t>
+          <t>99367</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121144</t>
+          <t>121387</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,65%</t>
         </is>
       </c>
     </row>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2297</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>712</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6775</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>894</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>7766</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>588</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6709</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12078</t>
+          <t>12259</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14366</t>
+          <t>14784</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>11068</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23430</t>
+          <t>23214</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12466</t>
+          <t>13016</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24454</t>
+          <t>24207</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16473</t>
+          <t>15762</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29733</t>
+          <t>29627</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32260</t>
+          <t>31361</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50397</t>
+          <t>51129</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37820</t>
+          <t>37319</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51044</t>
+          <t>50696</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33962</t>
+          <t>34113</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47934</t>
+          <t>49392</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>75784</t>
+          <t>76123</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>95992</t>
+          <t>96109</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,22%</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>818</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>197</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15586</t>
+          <t>15951</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29760</t>
+          <t>30359</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18009</t>
+          <t>17532</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>25398</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43072</t>
+          <t>43017</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25248</t>
+          <t>24767</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41211</t>
+          <t>41321</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25787</t>
+          <t>25334</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>40808</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>54991</t>
+          <t>54670</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>77175</t>
+          <t>77635</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>37,02%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42070</t>
+          <t>42274</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59963</t>
+          <t>59857</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45772</t>
+          <t>47006</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>62930</t>
+          <t>63655</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>94048</t>
+          <t>92622</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>116660</t>
+          <t>117684</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>56,11%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>518</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8331</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>11161</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18473</t>
+          <t>16675</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10126</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>23278</t>
+          <t>23469</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>42554</t>
+          <t>42507</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>64711</t>
+          <t>65067</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26823</t>
+          <t>26752</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>47013</t>
+          <t>46731</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>74956</t>
+          <t>74868</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>103902</t>
+          <t>104570</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>97099</t>
+          <t>97561</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>126453</t>
+          <t>126715</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>96502</t>
+          <t>96617</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>126476</t>
+          <t>127728</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>201075</t>
+          <t>203354</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>243919</t>
+          <t>244731</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>169518</t>
+          <t>169591</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>201691</t>
+          <t>200138</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>182939</t>
+          <t>183255</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>215195</t>
+          <t>215066</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>361320</t>
+          <t>362627</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>407911</t>
+          <t>406179</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,56%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse triste en 2023 (tasa de respuesta: 99,59%)</t>
+          <t>Menores según la frecuencia de sentirse triste, percibida por el adulto en 2023 (tasa de respuesta: 99,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>708</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,82 +11674,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,27%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1686</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6135</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>4923</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1699</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>11775</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>1,2%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,5%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1686</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6161</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>4923</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1855</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>11817</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>525</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>6165</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>24033</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>32414</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14527</t>
+          <t>12888</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16363</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6823</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18335</t>
+          <t>17853</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22805</t>
+          <t>21740</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17126</t>
+          <t>16848</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35972</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32176</t>
+          <t>31897</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45071</t>
+          <t>44489</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43285</t>
+          <t>44146</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67173</t>
+          <t>67497</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79304</t>
+          <t>80068</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>108494</t>
+          <t>108065</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,03%</t>
         </is>
       </c>
     </row>
@@ -12346,7 +12346,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10458</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13039</t>
+          <t>12655</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>705</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8798</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1391</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>8802</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>12720</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17513</t>
+          <t>17423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11380</t>
+          <t>10789</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24152</t>
+          <t>24518</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33354</t>
+          <t>32654</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57476</t>
+          <t>56861</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48117</t>
+          <t>48614</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74787</t>
+          <t>78443</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64905</t>
+          <t>65708</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>79160</t>
+          <t>80079</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77930</t>
+          <t>78851</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102390</t>
+          <t>103112</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>148876</t>
+          <t>147689</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>177515</t>
+          <t>178048</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,24%</t>
         </is>
       </c>
     </row>
@@ -13028,7 +13028,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5754</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>639</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>6650</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -13141,7 +13141,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13226,7 +13226,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>10851</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22132</t>
+          <t>24952</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30721</t>
+          <t>29340</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33358</t>
+          <t>31215</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11045</t>
+          <t>10772</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26394</t>
+          <t>25568</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24580</t>
+          <t>23952</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52428</t>
+          <t>51785</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>77723</t>
+          <t>78616</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>106490</t>
+          <t>105596</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>67732</t>
+          <t>66842</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89397</t>
+          <t>90248</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>155396</t>
+          <t>153136</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>191261</t>
+          <t>190361</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,57%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>724</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11677</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>569</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>893</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7733</t>
+          <t>8503</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>12871</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12719</t>
+          <t>12704</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8501</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21464</t>
+          <t>21596</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14021,7 +14021,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16597</t>
+          <t>16652</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31396</t>
+          <t>30820</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>11455</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25002</t>
+          <t>26821</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32231</t>
+          <t>31533</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51899</t>
+          <t>51341</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>51024</t>
+          <t>51651</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>67559</t>
+          <t>68178</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>59306</t>
+          <t>57359</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>75950</t>
+          <t>74463</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>114569</t>
+          <t>114640</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>137280</t>
+          <t>137768</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,94%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17101</t>
+          <t>17348</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17851</t>
+          <t>18347</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14442,7 +14442,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13186</t>
+          <t>12902</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30956</t>
+          <t>29583</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32148</t>
+          <t>37220</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>37784</t>
+          <t>38816</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11487</t>
+          <t>11268</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25810</t>
+          <t>26666</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>19976</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>46137</t>
+          <t>46320</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>34921</t>
+          <t>35443</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>64178</t>
+          <t>66141</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>54850</t>
+          <t>52506</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>88053</t>
+          <t>87359</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>76082</t>
+          <t>76576</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>112606</t>
+          <t>112341</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>138456</t>
+          <t>138418</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>188247</t>
+          <t>189998</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>244233</t>
+          <t>245503</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>286605</t>
+          <t>288172</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>274669</t>
+          <t>272431</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>319783</t>
+          <t>316742</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>530478</t>
+          <t>531507</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>591721</t>
+          <t>592532</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,34%</t>
         </is>
       </c>
     </row>
